--- a/data/excel/sectors.xlsx
+++ b/data/excel/sectors.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F93"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,7 +459,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.8100000000000001</v>
+        <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -487,16 +487,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Power &amp; Utilities</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -515,16 +515,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Conglomerates</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -543,16 +543,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Renewable Energy</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -571,16 +571,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2.12</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -599,16 +599,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Power &amp; Utilities</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3.01</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -632,11 +632,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cement</t>
+          <t>Construction Materials</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2.82</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -683,16 +683,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Paints &amp; Coatings</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -706,21 +706,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Services</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Gas Distribution</t>
+          <t>Consumer Services</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -739,16 +739,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Private Banks</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.97</v>
+        <v>1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -767,16 +767,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Two Wheelers</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -790,21 +790,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Diversified Financials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2.12</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -818,21 +818,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Holding Companies</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3.36</v>
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -846,21 +846,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Consumer Finance</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.78</v>
+        <v>1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -879,16 +879,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Public Sector Banks</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.27</v>
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -907,16 +907,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Defence Electronics</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3.65</v>
+        <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -930,21 +930,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -958,21 +958,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Telecommunication</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Telecommunication</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.24</v>
+        <v>1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -991,16 +991,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Auto Ancillaries</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2.82</v>
+        <v>1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1014,21 +1014,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Refining</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2.57</v>
+        <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.66</v>
+        <v>1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1075,16 +1075,16 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Public Sector Banks</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2.96</v>
+        <v>1</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1103,16 +1103,16 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Consumer Finance</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3.94</v>
+        <v>1</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1136,11 +1136,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1159,16 +1159,16 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mining &amp; Metals</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.46</v>
+        <v>1</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1182,21 +1182,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Personal Products</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1210,21 +1210,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Realty</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Realty</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3.75</v>
+        <v>1</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1238,21 +1238,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2.86</v>
+        <v>1</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1266,21 +1266,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3.07</v>
+        <v>1</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1294,25 +1294,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
     </row>
@@ -1322,21 +1322,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Services</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Two Wheelers</t>
+          <t>Consumer Services</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3.13</v>
+        <v>1</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1360,11 +1360,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Gas Distribution</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3.12</v>
+        <v>1</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1383,16 +1383,16 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Personal Products</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1411,20 +1411,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Diversified Industrials</t>
+          <t>Construction Materials</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2.61</v>
+        <v>1</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
     </row>
@@ -1434,21 +1434,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Defence &amp; Aerospace</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Consumer Electricals</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1490,21 +1490,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1518,21 +1518,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Private Banks</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1546,21 +1546,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Life Insurance</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1574,21 +1574,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Two Wheelers</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.26</v>
+        <v>1</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1602,21 +1602,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.64</v>
+        <v>1</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1630,25 +1630,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
     </row>
@@ -1658,21 +1658,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Private Banks</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3.87</v>
+        <v>1</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1686,21 +1686,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>General Insurance</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3.51</v>
+        <v>1</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1714,21 +1714,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Life Insurance</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2.47</v>
+        <v>1</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1742,21 +1742,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Services</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Consumer Services</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3.03</v>
+        <v>1</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1770,21 +1770,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Private Banks</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2.54</v>
+        <v>1</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1798,21 +1798,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3.37</v>
+        <v>1</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -1826,25 +1826,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Refining</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.27</v>
+        <v>1</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
     </row>
@@ -1854,25 +1854,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Travel &amp; Tourism</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3.97</v>
+        <v>1</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
     </row>
@@ -1882,21 +1882,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Speciality Finance</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4.33</v>
+        <v>1</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -1910,21 +1910,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Diversified FMCG</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1.39</v>
+        <v>1</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -1938,21 +1938,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1.41</v>
+        <v>1</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -1966,25 +1966,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Diversified Financials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
     </row>
@@ -1994,25 +1994,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>LTM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Power &amp; Utilities</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
     </row>
@@ -2022,21 +2022,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4.49</v>
+        <v>1</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2050,21 +2050,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Realty</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Private Banks</t>
+          <t>Realty</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3.47</v>
+        <v>1</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2078,21 +2078,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Life Insurance</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2.18</v>
+        <v>1</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2106,21 +2106,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1.59</v>
+        <v>1</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2134,21 +2134,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Engineering &amp; Construction</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3.03</v>
+        <v>1</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2162,21 +2162,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LTIM</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2.64</v>
+        <v>1</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2190,21 +2190,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3.95</v>
+        <v>1</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2218,25 +2218,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
     </row>
@@ -2246,21 +2246,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Auto Ancillaries</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3.39</v>
+        <v>1</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2274,21 +2274,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Internet &amp; Platforms</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4.44</v>
+        <v>1</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2302,21 +2302,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2330,21 +2330,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Power &amp; Utilities</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2358,21 +2358,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Power &amp; Utilities</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4.04</v>
+        <v>1</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2386,21 +2386,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4.49</v>
+        <v>1</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2414,21 +2414,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Speciality Finance</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2.15</v>
+        <v>1</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2442,21 +2442,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Specialty Chemicals</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2.15</v>
+        <v>1</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2470,21 +2470,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Public Sector Banks</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3.82</v>
+        <v>1</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -2498,21 +2498,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Power Transmission</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4.12</v>
+        <v>1</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2526,21 +2526,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Speciality Finance</t>
+          <t>Construction Materials</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1.78</v>
+        <v>1</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -2554,21 +2554,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Conglomerates</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4.24</v>
+        <v>1</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -2582,21 +2582,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>ENRIN</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Life Insurance</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3.16</v>
+        <v>1</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2610,21 +2610,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Public Sector Banks</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -2638,21 +2638,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Cement</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2.86</v>
+        <v>1</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -2666,21 +2666,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Consumer Finance</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -2694,21 +2694,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -2722,21 +2722,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -2750,21 +2750,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>TATACAP</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Food &amp; Beverages</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -2778,21 +2778,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TATAMOTORS</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -2806,25 +2806,25 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Power &amp; Utilities</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4.19</v>
+        <v>1</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
     </row>
@@ -2834,25 +2834,25 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>TMCV</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
     </row>
@@ -2862,21 +2862,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>TMPV</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -2890,21 +2890,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2.39</v>
+        <v>1</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -2918,21 +2918,21 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Gems &amp; Jewellery</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2.38</v>
+        <v>1</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -2946,21 +2946,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -2974,21 +2974,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -3002,23 +3002,247 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Two Wheelers</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2.16</v>
+        <v>1</v>
       </c>
       <c r="F93" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>TRENT</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
